--- a/personal.xlsx
+++ b/personal.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coltradecomco-my.sharepoint.com/personal/tecnologia_coltrade_com_co/Documents/Coltrade/BUSINESS INTELLIGENCE/02. AREAS/DATA/Julian Estif Herreno Palacios/xppcoltrade/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_1D76B689DA1352A260DD587221954A9F3BA0334B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD658FDB-D90B-4700-99BE-9DEE6B40BE4B}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_1D76B689DA1352A260DD587221954A9F3BA0334B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0541A908-D15C-484A-AEC3-5CB893151133}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="225">
   <si>
     <t xml:space="preserve">Nombre </t>
   </si>
@@ -538,9 +537,6 @@
   </si>
   <si>
     <t>Logistics  Analyst  Senior</t>
-  </si>
-  <si>
-    <t>LOGISTICS</t>
   </si>
   <si>
     <t>velaedver@supli.tech</t>
@@ -781,7 +777,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:K66" totalsRowShown="0">
-  <autoFilter ref="A1:K66" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A1:K66" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nombre "/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Cargo "/>
@@ -1116,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
@@ -1132,7 +1128,7 @@
     <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1167,7 +1163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1201,12 +1197,8 @@
       <c r="K2">
         <v>1989</v>
       </c>
-      <c r="M2" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>mejiafabio@supli.tech</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1240,12 +1232,8 @@
       <c r="K3">
         <v>1990</v>
       </c>
-      <c r="M3" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>ordonezjuan@supli.tech</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1279,12 +1267,8 @@
       <c r="K4">
         <v>1993</v>
       </c>
-      <c r="M4" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>ayalalaura@supli.tech</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1318,12 +1302,8 @@
       <c r="K5">
         <v>1979</v>
       </c>
-      <c r="M5" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>fonnegraheidi@supli.tech</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -1357,12 +1337,8 @@
       <c r="K6">
         <v>1997</v>
       </c>
-      <c r="M6" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>ramirezjulian@supli.tech</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -1396,12 +1372,8 @@
       <c r="K7">
         <v>1989</v>
       </c>
-      <c r="M7" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>estradajessica@supli.tech</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -1435,12 +1407,8 @@
       <c r="K8">
         <v>1984</v>
       </c>
-      <c r="M8" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>prietojaneth@supli.tech</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -1474,12 +1442,8 @@
       <c r="K9">
         <v>1994</v>
       </c>
-      <c r="M9" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>mezapaula@supli.tech</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -1513,12 +1477,8 @@
       <c r="K10">
         <v>1999</v>
       </c>
-      <c r="M10" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>arzayusnicolas@supli.tech</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -1552,12 +1512,8 @@
       <c r="K11">
         <v>1993</v>
       </c>
-      <c r="M11" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>sanchezandres@supli.tech</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -1591,12 +1547,8 @@
       <c r="K12">
         <v>2000</v>
       </c>
-      <c r="M12" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>cajamarcajuan@supli.tech</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -1622,7 +1574,7 @@
         <v>3023301463</v>
       </c>
       <c r="I13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J13">
         <v>52</v>
@@ -1630,12 +1582,8 @@
       <c r="K13">
         <v>1974</v>
       </c>
-      <c r="M13" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>yofrajilp@gmail.com</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -1669,12 +1617,8 @@
       <c r="K14">
         <v>1990</v>
       </c>
-      <c r="M14" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>rodriguezangie@supli.tech</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -1700,7 +1644,7 @@
         <v>3160542594</v>
       </c>
       <c r="I15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J15">
         <v>51</v>
@@ -1708,18 +1652,17 @@
       <c r="K15">
         <v>1975</v>
       </c>
-      <c r="M15" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>alejandroet@gmail.com</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>77</v>
       </c>
       <c r="B16" t="s">
         <v>78</v>
       </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
       <c r="D16" t="s">
         <v>79</v>
       </c>
@@ -1744,18 +1687,17 @@
       <c r="K16">
         <v>1996</v>
       </c>
-      <c r="M16" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>correadaniel@supli.tech</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>82</v>
       </c>
       <c r="B17" t="s">
         <v>83</v>
       </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
       <c r="D17" t="s">
         <v>79</v>
       </c>
@@ -1771,7 +1713,7 @@
       <c r="H17">
         <v>3027760395</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="1" t="s">
         <v>85</v>
       </c>
       <c r="J17">
@@ -1780,12 +1722,8 @@
       <c r="K17">
         <v>2002</v>
       </c>
-      <c r="M17" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>herrenojulian@supli.tech</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -1811,7 +1749,7 @@
         <v>3144931691</v>
       </c>
       <c r="I18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J18">
         <v>49</v>
@@ -1819,12 +1757,8 @@
       <c r="K18">
         <v>1977</v>
       </c>
-      <c r="M18" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>heidysanjuan@hotmail.com</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>87</v>
       </c>
@@ -1858,12 +1792,8 @@
       <c r="K19">
         <v>2001</v>
       </c>
-      <c r="M19" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>gutierrezfred@supli.tech</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -1897,12 +1827,8 @@
       <c r="K20">
         <v>1981</v>
       </c>
-      <c r="M20" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>yyyppp81@hotmail.com</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -1936,12 +1862,8 @@
       <c r="K21">
         <v>1982</v>
       </c>
-      <c r="M21" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>mercedesbeleno97@gmail.com</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -1967,7 +1889,7 @@
         <v>3102448443</v>
       </c>
       <c r="I22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J22">
         <v>42</v>
@@ -1975,18 +1897,17 @@
       <c r="K22">
         <v>1984</v>
       </c>
-      <c r="M22" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>merysierra0107@gmail.com</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>97</v>
       </c>
       <c r="B23" t="s">
         <v>98</v>
       </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
       <c r="D23" t="s">
         <v>59</v>
       </c>
@@ -2011,12 +1932,8 @@
       <c r="K23">
         <v>1997</v>
       </c>
-      <c r="M23" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>quinterojazbleydy@coltrade.com.co</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>100</v>
       </c>
@@ -2042,7 +1959,7 @@
         <v>3204533004</v>
       </c>
       <c r="I24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J24">
         <v>40</v>
@@ -2050,12 +1967,8 @@
       <c r="K24">
         <v>1986</v>
       </c>
-      <c r="M24" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>mitashiro1108@hotmail.com</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -2081,7 +1994,7 @@
         <v>3112885516</v>
       </c>
       <c r="I25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J25">
         <v>39</v>
@@ -2089,12 +2002,8 @@
       <c r="K25">
         <v>1987</v>
       </c>
-      <c r="M25" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>jeduardoes@hotmail.com</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>103</v>
       </c>
@@ -2128,12 +2037,8 @@
       <c r="K26">
         <v>1984</v>
       </c>
-      <c r="M26" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>vargasmarco@supli.tech</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>105</v>
       </c>
@@ -2159,7 +2064,7 @@
         <v>3016496940</v>
       </c>
       <c r="I27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J27">
         <v>38</v>
@@ -2167,12 +2072,8 @@
       <c r="K27">
         <v>1988</v>
       </c>
-      <c r="M27" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>johnemm88@gmail.com</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>106</v>
       </c>
@@ -2206,12 +2107,8 @@
       <c r="K28">
         <v>1988</v>
       </c>
-      <c r="M28" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>lopezcindy@supli.tech</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>109</v>
       </c>
@@ -2237,7 +2134,7 @@
         <v>3143994492</v>
       </c>
       <c r="I29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J29">
         <v>38</v>
@@ -2245,12 +2142,8 @@
       <c r="K29">
         <v>1988</v>
       </c>
-      <c r="M29" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>urzola55@gmail.com</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>110</v>
       </c>
@@ -2284,12 +2177,8 @@
       <c r="K30">
         <v>1995</v>
       </c>
-      <c r="M30" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>avilagerman@supli.tech</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>114</v>
       </c>
@@ -2323,12 +2212,8 @@
       <c r="K31">
         <v>1995</v>
       </c>
-      <c r="M31" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>rodriguezrobert@supli.tech</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -2354,7 +2239,7 @@
         <v>3228470057</v>
       </c>
       <c r="I32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J32">
         <v>35</v>
@@ -2362,12 +2247,8 @@
       <c r="K32">
         <v>1991</v>
       </c>
-      <c r="M32" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>diana_guevara91@hotmail.com</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>119</v>
       </c>
@@ -2401,12 +2282,8 @@
       <c r="K33">
         <v>1994</v>
       </c>
-      <c r="M33" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>rodriguezandrea@supli.tech</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>123</v>
       </c>
@@ -2440,12 +2317,8 @@
       <c r="K34">
         <v>1982</v>
       </c>
-      <c r="M34" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>montealegrewills@supli.tech</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>127</v>
       </c>
@@ -2471,7 +2344,7 @@
         <v>3505008023</v>
       </c>
       <c r="I35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J35">
         <v>35</v>
@@ -2479,12 +2352,8 @@
       <c r="K35">
         <v>1991</v>
       </c>
-      <c r="M35" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>vivianaacosta.2115@gmail.com</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>128</v>
       </c>
@@ -2518,12 +2387,8 @@
       <c r="K36">
         <v>1993</v>
       </c>
-      <c r="M36" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>calderonlorena@supli.tech</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>133</v>
       </c>
@@ -2549,7 +2414,7 @@
         <v>3244899145</v>
       </c>
       <c r="I37" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J37">
         <v>35</v>
@@ -2557,12 +2422,8 @@
       <c r="K37">
         <v>1991</v>
       </c>
-      <c r="M37" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>jbsiete22@gmail.com</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>134</v>
       </c>
@@ -2596,12 +2457,8 @@
       <c r="K38">
         <v>1991</v>
       </c>
-      <c r="M38" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>jjj.asneth@hotmail.com</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>136</v>
       </c>
@@ -2627,7 +2484,7 @@
         <v>3004924299</v>
       </c>
       <c r="I39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J39">
         <v>35</v>
@@ -2635,12 +2492,8 @@
       <c r="K39">
         <v>1991</v>
       </c>
-      <c r="M39" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>smithjaimesnieto123@gmail.com</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>137</v>
       </c>
@@ -2674,12 +2527,8 @@
       <c r="K40">
         <v>1991</v>
       </c>
-      <c r="M40" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>aleja.91suarez@gmail.com</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -2713,12 +2562,8 @@
       <c r="K41">
         <v>1993</v>
       </c>
-      <c r="M41" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>barbosaliseth@supli.tech</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>144</v>
       </c>
@@ -2752,12 +2597,8 @@
       <c r="K42">
         <v>2000</v>
       </c>
-      <c r="M42" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>martinangie@supli.tech</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>149</v>
       </c>
@@ -2791,12 +2632,8 @@
       <c r="K43">
         <v>2000</v>
       </c>
-      <c r="M43" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>rodriguezjorgea@supli.tech</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>153</v>
       </c>
@@ -2822,7 +2659,7 @@
         <v>3143571594</v>
       </c>
       <c r="I44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J44">
         <v>34</v>
@@ -2830,12 +2667,8 @@
       <c r="K44">
         <v>1992</v>
       </c>
-      <c r="M44" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>mejiageraldine218@gmail.com</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>154</v>
       </c>
@@ -2861,7 +2694,7 @@
         <v>3044325494</v>
       </c>
       <c r="I45" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J45">
         <v>32</v>
@@ -2869,12 +2702,8 @@
       <c r="K45">
         <v>1994</v>
       </c>
-      <c r="M45" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>mariabpt1994@gmail.com</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>155</v>
       </c>
@@ -2900,7 +2729,7 @@
         <v>3197728701</v>
       </c>
       <c r="I46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J46">
         <v>31</v>
@@ -2908,12 +2737,8 @@
       <c r="K46">
         <v>1995</v>
       </c>
-      <c r="M46" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>daniela19032015bastidas@gmail.com</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>156</v>
       </c>
@@ -2939,7 +2764,7 @@
         <v>3232049403</v>
       </c>
       <c r="I47" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J47">
         <v>30</v>
@@ -2947,12 +2772,8 @@
       <c r="K47">
         <v>1996</v>
       </c>
-      <c r="M47" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>dexysierra13@gmail.com</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>157</v>
       </c>
@@ -2978,7 +2799,7 @@
         <v>3125263515</v>
       </c>
       <c r="I48" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J48">
         <v>28</v>
@@ -2986,12 +2807,8 @@
       <c r="K48">
         <v>1998</v>
       </c>
-      <c r="M48" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>ealexandervo06@gmail.com</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>158</v>
       </c>
@@ -3025,12 +2842,8 @@
       <c r="K49">
         <v>2004</v>
       </c>
-      <c r="M49" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>fonsecajair@supli.tech</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>161</v>
       </c>
@@ -3056,7 +2869,7 @@
         <v>3172659751</v>
       </c>
       <c r="I50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J50">
         <v>28</v>
@@ -3064,12 +2877,8 @@
       <c r="K50">
         <v>1998</v>
       </c>
-      <c r="M50" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>lic.carloslealrojas@gmail.com</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>162</v>
       </c>
@@ -3103,12 +2912,8 @@
       <c r="K51">
         <v>1978</v>
       </c>
-      <c r="M51" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>munozfabian@supli.tech</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>166</v>
       </c>
@@ -3130,11 +2935,11 @@
       <c r="G52" t="s">
         <v>47</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52">
+        <v>3142327562</v>
+      </c>
+      <c r="I52" t="s">
         <v>168</v>
-      </c>
-      <c r="I52" t="s">
-        <v>169</v>
       </c>
       <c r="J52">
         <v>29</v>
@@ -3142,14 +2947,10 @@
       <c r="K52">
         <v>1997</v>
       </c>
-      <c r="M52" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>velaedver@supli.tech</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B53" t="s">
         <v>67</v>
@@ -3173,7 +2974,7 @@
         <v>3014890132</v>
       </c>
       <c r="I53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J53">
         <v>26</v>
@@ -3181,14 +2982,10 @@
       <c r="K53">
         <v>2000</v>
       </c>
-      <c r="M53" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>juancamilojc5008@gmail.com</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B54" t="s">
         <v>67</v>
@@ -3212,7 +3009,7 @@
         <v>3332338132</v>
       </c>
       <c r="I54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J54">
         <v>25</v>
@@ -3220,14 +3017,10 @@
       <c r="K54">
         <v>2001</v>
       </c>
-      <c r="M54" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>yeimyandreaj@gmail.com</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B55" t="s">
         <v>68</v>
@@ -3251,7 +3044,7 @@
         <v>3227372779</v>
       </c>
       <c r="I55" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J55">
         <v>23</v>
@@ -3259,14 +3052,10 @@
       <c r="K55">
         <v>2003</v>
       </c>
-      <c r="M55" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>ellenarrietaredondo@gmail.com</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B56" t="s">
         <v>67</v>
@@ -3290,7 +3079,7 @@
         <v>3142038457</v>
       </c>
       <c r="I56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J56">
         <v>23</v>
@@ -3298,14 +3087,10 @@
       <c r="K56">
         <v>2003</v>
       </c>
-      <c r="M56" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>yulianbartolo2003@gmail.com</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B57" t="s">
         <v>67</v>
@@ -3329,7 +3114,7 @@
         <v>3008498256</v>
       </c>
       <c r="I57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J57">
         <v>23</v>
@@ -3337,14 +3122,10 @@
       <c r="K57">
         <v>2003</v>
       </c>
-      <c r="M57" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>alisonfula9@gmail.com</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
@@ -3368,7 +3149,7 @@
         <v>3227766903</v>
       </c>
       <c r="I58" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J58">
         <v>22</v>
@@ -3376,14 +3157,10 @@
       <c r="K58">
         <v>2004</v>
       </c>
-      <c r="M58" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>jyesica40@gmail.com</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B59" t="s">
         <v>67</v>
@@ -3407,7 +3184,7 @@
         <v>3216549288</v>
       </c>
       <c r="I59" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J59">
         <v>21</v>
@@ -3415,14 +3192,10 @@
       <c r="K59">
         <v>2005</v>
       </c>
-      <c r="M59" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>karecontreras57@gmail.com</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B60" t="s">
         <v>67</v>
@@ -3446,7 +3219,7 @@
         <v>3027022539</v>
       </c>
       <c r="I60" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J60">
         <v>21</v>
@@ -3454,17 +3227,13 @@
       <c r="K60">
         <v>2005</v>
       </c>
-      <c r="M60" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>ab9654507@gmail.com</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61" t="s">
         <v>181</v>
-      </c>
-      <c r="B61" t="s">
-        <v>182</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
@@ -3485,7 +3254,7 @@
         <v>3206226576</v>
       </c>
       <c r="I61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J61">
         <v>36</v>
@@ -3493,14 +3262,10 @@
       <c r="K61">
         <v>1990</v>
       </c>
-      <c r="M61" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>reyeslida@supli.tech</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B62" t="s">
         <v>67</v>
@@ -3524,7 +3289,7 @@
         <v>3057828524</v>
       </c>
       <c r="I62" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J62">
         <v>18</v>
@@ -3532,17 +3297,13 @@
       <c r="K62">
         <v>2008</v>
       </c>
-      <c r="M62" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>thomasb1219q@gmail.com</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>185</v>
+      </c>
+      <c r="B63" t="s">
         <v>186</v>
-      </c>
-      <c r="B63" t="s">
-        <v>187</v>
       </c>
       <c r="C63" t="s">
         <v>18</v>
@@ -3551,7 +3312,7 @@
         <v>41</v>
       </c>
       <c r="E63" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F63" t="s">
         <v>20</v>
@@ -3563,7 +3324,7 @@
         <v>51941882356</v>
       </c>
       <c r="I63" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J63">
         <v>50</v>
@@ -3571,17 +3332,13 @@
       <c r="K63">
         <v>1976</v>
       </c>
-      <c r="M63" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>jordanjulio@supli.tech</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>189</v>
+      </c>
+      <c r="B64" t="s">
         <v>190</v>
-      </c>
-      <c r="B64" t="s">
-        <v>191</v>
       </c>
       <c r="C64" t="s">
         <v>18</v>
@@ -3590,7 +3347,7 @@
         <v>71</v>
       </c>
       <c r="E64" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F64" t="s">
         <v>20</v>
@@ -3602,7 +3359,7 @@
         <v>3015454907</v>
       </c>
       <c r="I64" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J64">
         <v>31</v>
@@ -3610,17 +3367,13 @@
       <c r="K64">
         <v>1995</v>
       </c>
-      <c r="M64" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>mendezluisa@supli.tech</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>193</v>
+      </c>
+      <c r="B65" t="s">
         <v>194</v>
-      </c>
-      <c r="B65" t="s">
-        <v>195</v>
       </c>
       <c r="C65" t="s">
         <v>146</v>
@@ -3629,7 +3382,7 @@
         <v>147</v>
       </c>
       <c r="E65" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F65" t="s">
         <v>146</v>
@@ -3638,10 +3391,10 @@
         <v>147</v>
       </c>
       <c r="H65" t="s">
+        <v>195</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="J65">
         <v>34</v>
@@ -3649,17 +3402,13 @@
       <c r="K65">
         <v>1992</v>
       </c>
-      <c r="M65" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>vasquezjohana@supli.tech</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>197</v>
+      </c>
+      <c r="B66" t="s">
         <v>198</v>
-      </c>
-      <c r="B66" t="s">
-        <v>199</v>
       </c>
       <c r="C66" t="s">
         <v>18</v>
@@ -3668,7 +3417,7 @@
         <v>71</v>
       </c>
       <c r="E66" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F66" t="s">
         <v>20</v>
@@ -3677,39 +3426,27 @@
         <v>71</v>
       </c>
       <c r="H66" t="s">
+        <v>200</v>
+      </c>
+      <c r="I66" t="s">
         <v>201</v>
-      </c>
-      <c r="I66" t="s">
-        <v>202</v>
       </c>
       <c r="J66">
         <v>29</v>
       </c>
       <c r="K66">
         <v>1997</v>
-      </c>
-      <c r="M66" t="str">
-        <f>+LOWER(Tabla1[[#This Row],[CORREO ]])</f>
-        <v>novavaleria@supli.tech</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I42" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="I65" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="I17" r:id="rId3" xr:uid="{1186AE3D-998A-40F6-BF97-7E47D6700DAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>